--- a/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
@@ -726,14 +726,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45182.57899016439</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -774,26 +770,6 @@
     <row r="11" ht="41.25" customHeight="1" s="19">
       <c r="E11" s="8" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="19">
       <c r="A32" s="10" t="inlineStr">
         <is>
@@ -965,17 +941,6 @@
       </c>
       <c r="E41" s="2" t="n"/>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" s="3" t="n"/>
     </row>
@@ -984,19 +949,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
@@ -726,7 +726,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>

--- a/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
@@ -726,7 +726,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>

--- a/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
@@ -726,10 +726,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45266</v>
+        <v>45232.58379887719</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -770,6 +774,26 @@
     <row r="11" ht="41.25" customHeight="1" s="19">
       <c r="E11" s="8" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="19">
       <c r="A32" s="10" t="inlineStr">
         <is>
@@ -801,7 +825,7 @@
       </c>
       <c r="C33" s="18" t="n"/>
       <c r="D33" s="12" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="E33" s="2" t="n"/>
     </row>
@@ -818,7 +842,7 @@
       </c>
       <c r="C34" s="18" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>431.1</v>
+        <v>480</v>
       </c>
       <c r="E34" s="2" t="n"/>
     </row>
@@ -835,7 +859,7 @@
       </c>
       <c r="C35" s="18" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>460</v>
+        <v>509</v>
       </c>
       <c r="E35" s="2" t="n"/>
     </row>
@@ -852,7 +876,7 @@
       </c>
       <c r="C36" s="18" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>580</v>
+        <v>643</v>
       </c>
       <c r="E36" s="2" t="n"/>
     </row>
@@ -869,7 +893,7 @@
       </c>
       <c r="C37" s="18" t="n"/>
       <c r="D37" s="13" t="n">
-        <v>731</v>
+        <v>813</v>
       </c>
       <c r="E37" s="2" t="n"/>
     </row>
@@ -886,7 +910,7 @@
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="13" t="n">
-        <v>584.3</v>
+        <v>650</v>
       </c>
       <c r="E38" s="2" t="n"/>
     </row>
@@ -903,7 +927,7 @@
       </c>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="13" t="n">
-        <v>715</v>
+        <v>795</v>
       </c>
       <c r="E39" s="2" t="n"/>
     </row>
@@ -920,7 +944,7 @@
       </c>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="13" t="n">
-        <v>890.3</v>
+        <v>990</v>
       </c>
       <c r="E40" s="2" t="n"/>
     </row>
@@ -937,10 +961,21 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="13" t="n">
-        <v>1034</v>
+        <v>1150</v>
       </c>
       <c r="E41" s="2" t="n"/>
     </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" s="3" t="n"/>
     </row>
@@ -949,19 +984,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/mi/BURLETES AUTOADHESIVOS DISMAY.xlsx
@@ -726,14 +726,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45232.58379887719</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -774,26 +770,6 @@
     <row r="11" ht="41.25" customHeight="1" s="19">
       <c r="E11" s="8" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="19">
       <c r="A32" s="10" t="inlineStr">
         <is>
@@ -825,7 +801,7 @@
       </c>
       <c r="C33" s="18" t="n"/>
       <c r="D33" s="12" t="n">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="E33" s="2" t="n"/>
     </row>
@@ -842,7 +818,7 @@
       </c>
       <c r="C34" s="18" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>480</v>
+        <v>431.1</v>
       </c>
       <c r="E34" s="2" t="n"/>
     </row>
@@ -859,7 +835,7 @@
       </c>
       <c r="C35" s="18" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>509</v>
+        <v>460</v>
       </c>
       <c r="E35" s="2" t="n"/>
     </row>
@@ -876,7 +852,7 @@
       </c>
       <c r="C36" s="18" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>643</v>
+        <v>580</v>
       </c>
       <c r="E36" s="2" t="n"/>
     </row>
@@ -893,7 +869,7 @@
       </c>
       <c r="C37" s="18" t="n"/>
       <c r="D37" s="13" t="n">
-        <v>813</v>
+        <v>731</v>
       </c>
       <c r="E37" s="2" t="n"/>
     </row>
@@ -910,7 +886,7 @@
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="13" t="n">
-        <v>650</v>
+        <v>584.3</v>
       </c>
       <c r="E38" s="2" t="n"/>
     </row>
@@ -927,7 +903,7 @@
       </c>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="13" t="n">
-        <v>795</v>
+        <v>715</v>
       </c>
       <c r="E39" s="2" t="n"/>
     </row>
@@ -944,7 +920,7 @@
       </c>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="13" t="n">
-        <v>990</v>
+        <v>890.3</v>
       </c>
       <c r="E40" s="2" t="n"/>
     </row>
@@ -961,21 +937,10 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="13" t="n">
-        <v>1150</v>
+        <v>1034</v>
       </c>
       <c r="E41" s="2" t="n"/>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" s="3" t="n"/>
     </row>
@@ -984,19 +949,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
